--- a/data/trans_orig/IP09B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Provincia-trans_orig.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28267</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>26598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,23%</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>61,36%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14005</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12934</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>103352</t>
+          <t>103227</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>56498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,04%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13461</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>27968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79100</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>130081</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
